--- a/outputs/50521.xlsx
+++ b/outputs/50521.xlsx
@@ -116,20 +116,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -372,16 +368,16 @@
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3" t="n">
+      <c r="B4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="L4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="3" t="n">
+      <c r="L4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="0" t="n">
         <v>5</v>
       </c>
     </row>
@@ -389,16 +385,16 @@
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" s="3" t="n">
+      <c r="E5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="N5" s="0" t="n">
         <v>4</v>
       </c>
     </row>
@@ -406,16 +402,16 @@
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3" t="n">
+      <c r="B6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" s="0" t="n">
         <v>3</v>
       </c>
     </row>
